--- a/SGC-CKN/Excel/5310afda-d88c-493c-b776-ebc2f0815b5c_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-105_D800_13-03-2026.xlsx
+++ b/SGC-CKN/Excel/5310afda-d88c-493c-b776-ebc2f0815b5c_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-105_D800_13-03-2026.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="70">
   <si>
     <t>Dự án</t>
   </si>
   <si>
-    <t>Dự án số 1 khu đô thị trung tâm thành phố Thanh Hóa (Vinhomes Star City)</t>
+    <t>Star City Thanh Hóa</t>
   </si>
   <si>
     <t>Hạng mục</t>
@@ -38,10 +38,10 @@
     <t>P7-105</t>
   </si>
   <si>
-    <t>Biên bản số</t>
-  </si>
-  <si>
-    <t>M3-3.1.1.2.6</t>
+    <t>Tên Máy khoan</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Đường kính</t>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Đất san lấp</t>
+    <t>Đất san lấp / Cát san lấp</t>
   </si>
   <si>
     <t xml:space="preserve">19:55
@@ -106,9 +106,6 @@
 12/03/2026</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
@@ -122,7 +119,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha xám ghi, xám nâu, xám vàng TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">22:05
@@ -172,7 +169,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">02:40
@@ -182,7 +179,7 @@
     <t>9</t>
   </si>
   <si>
-    <t>TK-16.1. Cát xám, xám vàng, xám xanh, TT rất chặt</t>
+    <t>Cát xám, xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">03:40
@@ -195,9 +192,6 @@
     <t>10</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
-  </si>
-  <si>
     <t xml:space="preserve">04:40
 13/03/2026</t>
   </si>
@@ -205,7 +199,7 @@
     <t>11</t>
   </si>
   <si>
-    <t>Cuội đa màu sắc TT rất chặt</t>
+    <t>Cuội, sỏi, sạn cát, đá khoảng, đa sắc, TT chặt đến rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">09:45
@@ -1231,24 +1225,24 @@
         <v>2.06</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>31</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>29</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F12" s="9">
         <v>-2</v>
@@ -1266,24 +1260,24 @@
         <v>13</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="14" t="s">
+      <c r="D13" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="15" t="s">
         <v>35</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>36</v>
       </c>
       <c r="F13" s="13">
         <v>-8.5</v>
@@ -1301,24 +1295,24 @@
         <v>1.85</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="17" t="s">
+      <c r="D14" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="18" t="s">
         <v>38</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>39</v>
       </c>
       <c r="F14" s="16">
         <v>-10.5</v>
@@ -1336,24 +1330,24 @@
         <v>12</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="20" t="s">
+      <c r="D15" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="21" t="s">
         <v>41</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>42</v>
       </c>
       <c r="F15" s="19">
         <v>-18.5</v>
@@ -1371,24 +1365,24 @@
         <v>3.23</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="23" t="s">
+      <c r="D16" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" s="24" t="s">
         <v>44</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>45</v>
       </c>
       <c r="F16" s="22">
         <v>-22.8</v>
@@ -1406,24 +1400,24 @@
         <v>4.36</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="26" t="s">
+      <c r="D17" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="27" t="s">
         <v>47</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>48</v>
       </c>
       <c r="F17" s="25">
         <v>-26.8</v>
@@ -1441,24 +1435,24 @@
         <v>20</v>
       </c>
       <c r="K17" s="26" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="29" t="s">
+      <c r="D18" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" s="30" t="s">
         <v>50</v>
-      </c>
-      <c r="D18" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>51</v>
       </c>
       <c r="F18" s="28">
         <v>-36.8</v>
@@ -1476,24 +1470,24 @@
         <v>2.06</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="B19" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="32" t="s">
+      <c r="D19" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19" s="33" t="s">
         <v>53</v>
-      </c>
-      <c r="D19" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>54</v>
       </c>
       <c r="F19" s="31">
         <v>-39.2</v>
@@ -1511,24 +1505,24 @@
         <v>1.5</v>
       </c>
       <c r="K19" s="32" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" s="36" t="s">
         <v>56</v>
-      </c>
-      <c r="B20" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="35" t="s">
-        <v>57</v>
-      </c>
-      <c r="D20" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>58</v>
       </c>
       <c r="F20" s="34">
         <v>-40.7</v>
@@ -1546,24 +1540,24 @@
         <v>4</v>
       </c>
       <c r="K20" s="35" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" s="18" t="s">
         <v>59</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="E21" s="18" t="s">
-        <v>61</v>
       </c>
       <c r="F21" s="16">
         <v>-44.7</v>
@@ -1581,12 +1575,12 @@
         <v>1.13</v>
       </c>
       <c r="K21" s="17" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="37" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B24" s="37"/>
       <c r="C24" s="37"/>
@@ -1692,31 +1686,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1756,7 +1750,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1785,7 +1779,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" s="13">
         <v>1</v>
@@ -1814,7 +1808,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -1843,7 +1837,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
@@ -1872,7 +1866,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
@@ -1901,7 +1895,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1930,7 +1924,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1959,7 +1953,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
@@ -1988,7 +1982,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
@@ -2017,7 +2011,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D12" s="16">
         <v>1</v>
@@ -2040,13 +2034,13 @@
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="38" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="D13" s="39">
         <v>11</v>

--- a/SGC-CKN/Excel/5310afda-d88c-493c-b776-ebc2f0815b5c_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-105_D800_13-03-2026.xlsx
+++ b/SGC-CKN/Excel/5310afda-d88c-493c-b776-ebc2f0815b5c_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-105_D800_13-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="69">
   <si>
     <t>Dự án</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Tên Máy khoan</t>
   </si>
   <si>
-    <t/>
+    <t>SGCT-KCN0003</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -106,10 +106,13 @@
 12/03/2026</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">21:00
@@ -129,9 +132,6 @@
     <t>4</t>
   </si>
   <si>
-    <t>Sét xám trắng, xám xanh dẻo chảy</t>
-  </si>
-  <si>
     <t xml:space="preserve">22:45
 12/03/2026</t>
   </si>
@@ -149,7 +149,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, xám nâu TT chặt</t>
   </si>
   <si>
     <t xml:space="preserve">01:00
@@ -157,9 +157,6 @@
   </si>
   <si>
     <t>7</t>
-  </si>
-  <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
     <t xml:space="preserve">01:30
@@ -1225,24 +1222,24 @@
         <v>2.06</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>29</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F12" s="9">
         <v>-2</v>
@@ -1260,24 +1257,24 @@
         <v>13</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>32</v>
-      </c>
       <c r="E13" s="15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13" s="13">
         <v>-8.5</v>
@@ -1295,21 +1292,21 @@
         <v>1.85</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="18" t="s">
         <v>36</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>35</v>
       </c>
       <c r="E14" s="18" t="s">
         <v>38</v>
@@ -1330,7 +1327,7 @@
         <v>12</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1365,7 +1362,7 @@
         <v>3.23</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1400,187 +1397,187 @@
         <v>4.36</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="26" t="s">
+      <c r="B17" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="F17" s="25">
+      <c r="F17" s="22">
         <v>-26.8</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="22">
         <v>-36.8</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="22">
         <v>0.5</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="22">
         <v>10</v>
       </c>
       <c r="J17" s="12">
         <v>20</v>
       </c>
-      <c r="K17" s="26" t="s">
-        <v>9</v>
+      <c r="K17" s="23" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="29" t="s">
+      <c r="D18" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="F18" s="28">
+      <c r="F18" s="25">
         <v>-36.8</v>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="25">
         <v>-39.2</v>
       </c>
-      <c r="H18" s="28">
+      <c r="H18" s="25">
         <v>1.17</v>
       </c>
-      <c r="I18" s="28">
+      <c r="I18" s="25">
         <v>2.4</v>
       </c>
       <c r="J18" s="8">
         <v>2.06</v>
       </c>
-      <c r="K18" s="29" t="s">
-        <v>9</v>
+      <c r="K18" s="26" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="32" t="s">
+      <c r="D19" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="E19" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="33" t="s">
-        <v>50</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="F19" s="31">
+      <c r="F19" s="28">
         <v>-39.2</v>
       </c>
-      <c r="G19" s="31">
+      <c r="G19" s="28">
         <v>-40.7</v>
       </c>
-      <c r="H19" s="31">
+      <c r="H19" s="28">
         <v>1</v>
       </c>
-      <c r="I19" s="31">
+      <c r="I19" s="28">
         <v>1.5</v>
       </c>
       <c r="J19" s="8">
         <v>1.5</v>
       </c>
-      <c r="K19" s="32" t="s">
+      <c r="K19" s="29" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="31" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="34" t="s">
+      <c r="B20" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="B20" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="35" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="F20" s="34">
+      <c r="F20" s="31">
         <v>-40.7</v>
       </c>
-      <c r="G20" s="34">
+      <c r="G20" s="31">
         <v>-44.7</v>
       </c>
-      <c r="H20" s="34">
+      <c r="H20" s="31">
         <v>1</v>
       </c>
-      <c r="I20" s="34">
+      <c r="I20" s="31">
         <v>4</v>
       </c>
       <c r="J20" s="8">
         <v>4</v>
       </c>
-      <c r="K20" s="35" t="s">
-        <v>9</v>
+      <c r="K20" s="32" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="17" t="s">
+      <c r="D21" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="D21" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="E21" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="F21" s="16">
+      <c r="F21" s="34">
         <v>-44.7</v>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="34">
         <v>-50.45</v>
       </c>
-      <c r="H21" s="16">
+      <c r="H21" s="34">
         <v>5.08</v>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="34">
         <v>5.75</v>
       </c>
       <c r="J21" s="8">
         <v>1.13</v>
       </c>
-      <c r="K21" s="17" t="s">
-        <v>9</v>
+      <c r="K21" s="35" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="24" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="37" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B24" s="37"/>
       <c r="C24" s="37"/>
@@ -1673,7 +1670,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1686,31 +1683,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1750,7 +1747,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1779,7 +1776,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" s="13">
         <v>1</v>
@@ -1808,7 +1805,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -1869,22 +1866,22 @@
         <v>43</v>
       </c>
       <c r="D7" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="22">
         <v>-22.8</v>
       </c>
       <c r="F7" s="22">
-        <v>-26.8</v>
+        <v>-36.8</v>
       </c>
       <c r="G7" s="22">
-        <v>0.92</v>
+        <v>1.42</v>
       </c>
       <c r="H7" s="22">
-        <v>4</v>
-      </c>
-      <c r="I7" s="8">
-        <v>4.36</v>
+        <v>14</v>
+      </c>
+      <c r="I7" s="12">
+        <v>9.88</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1895,25 +1892,25 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>-26.8</v>
+        <v>-36.8</v>
       </c>
       <c r="F8" s="25">
-        <v>-36.8</v>
+        <v>-39.2</v>
       </c>
       <c r="G8" s="25">
-        <v>0.5</v>
+        <v>1.17</v>
       </c>
       <c r="H8" s="25">
-        <v>10</v>
-      </c>
-      <c r="I8" s="12">
-        <v>20</v>
+        <v>2.4</v>
+      </c>
+      <c r="I8" s="8">
+        <v>2.06</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1924,25 +1921,25 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-36.8</v>
+        <v>-39.2</v>
       </c>
       <c r="F9" s="28">
-        <v>-39.2</v>
+        <v>-40.7</v>
       </c>
       <c r="G9" s="28">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="H9" s="28">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="I9" s="8">
-        <v>2.06</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1953,25 +1950,25 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
       </c>
       <c r="E10" s="31">
-        <v>-39.2</v>
+        <v>-40.7</v>
       </c>
       <c r="F10" s="31">
-        <v>-40.7</v>
+        <v>-44.7</v>
       </c>
       <c r="G10" s="31">
         <v>1</v>
       </c>
       <c r="H10" s="31">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="I10" s="8">
-        <v>1.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1982,82 +1979,53 @@
         <v>11</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
       </c>
       <c r="E11" s="34">
-        <v>-40.7</v>
+        <v>-44.7</v>
       </c>
       <c r="F11" s="34">
-        <v>-44.7</v>
+        <v>-50.45</v>
       </c>
       <c r="G11" s="34">
-        <v>1</v>
+        <v>5.08</v>
       </c>
       <c r="H11" s="34">
-        <v>4</v>
+        <v>5.75</v>
       </c>
       <c r="I11" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="16">
-        <v>11</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="D12" s="16">
-        <v>1</v>
-      </c>
-      <c r="E12" s="16">
-        <v>-44.7</v>
-      </c>
-      <c r="F12" s="16">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="39">
+        <v>11</v>
+      </c>
+      <c r="E12" s="39">
+        <v>-0.8</v>
+      </c>
+      <c r="F12" s="39">
         <v>-50.45</v>
       </c>
-      <c r="G12" s="16">
-        <v>5.08</v>
-      </c>
-      <c r="H12" s="16">
-        <v>5.75</v>
-      </c>
-      <c r="I12" s="8">
-        <v>1.13</v>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="38" t="s">
-        <v>69</v>
-      </c>
-      <c r="B13" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="39">
-        <v>11</v>
-      </c>
-      <c r="E13" s="39">
-        <v>-0.8</v>
-      </c>
-      <c r="F13" s="39">
-        <v>-50.45</v>
-      </c>
-      <c r="G13" s="39">
+      <c r="G12" s="39">
         <v>13.83</v>
       </c>
-      <c r="H13" s="39">
+      <c r="H12" s="39">
         <v>49.65</v>
       </c>
-      <c r="I13" s="39">
+      <c r="I12" s="39">
         <v>3.59</v>
       </c>
     </row>
